--- a/data/carriers_data/biomass/biomass_prices.xlsx
+++ b/data/carriers_data/biomass/biomass_prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\plants_data\carriers_data\biomass\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\carriers_data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21839AC-50A2-4B71-8997-3A791597DDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="4" r:id="rId1"/>

--- a/data/carriers_data/biomass/biomass_prices.xlsx
+++ b/data/carriers_data/biomass/biomass_prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\data\carriers_data\biomass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21839AC-50A2-4B71-8997-3A791597DDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBBCD7C-161E-4424-A4F8-53EF555B62AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="4" r:id="rId1"/>
@@ -18,10 +18,21 @@
     <sheet name="ENS_Med" sheetId="2" r:id="rId3"/>
     <sheet name="ENS_High" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -366,9 +377,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA017BC-1F0B-4150-9932-58336370810C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -381,9 +392,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -397,7 +408,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -414,7 +425,7 @@
         <v>1.7997597759999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -431,7 +442,7 @@
         <v>3.819</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -456,9 +467,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD98E45F-EEB3-4F00-B435-84ED2BD9104F}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -472,7 +483,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -489,7 +500,7 @@
         <v>1.67717085</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -506,7 +517,7 @@
         <v>3.508</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -531,9 +542,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F625CA6D-F24C-4084-A44C-75DED3A76FF6}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>2020</v>
       </c>
@@ -547,7 +558,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -564,7 +575,7 @@
         <v>1.4932874629999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -581,7 +592,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
